--- a/database/event/7524/event_7524_evp_summary.xlsx
+++ b/database/event/7524/event_7524_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.6241</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5.8825</v>
       </c>
       <c r="D2" t="n">
         <v>3.8705</v>
@@ -545,7 +545,7 @@
         <v>7.699</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.2629</v>
       </c>
       <c r="D3" t="n">
         <v>2.6889</v>
@@ -591,7 +591,7 @@
         <v>5.5767</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.0878</v>
       </c>
       <c r="D4" t="n">
         <v>1.8315</v>
@@ -637,7 +637,7 @@
         <v>5.4387</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.0114</v>
       </c>
       <c r="D5" t="n">
         <v>1.7758</v>
@@ -683,7 +683,7 @@
         <v>5.1487</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.8508</v>
       </c>
       <c r="D6" t="n">
         <v>1.6586</v>
@@ -729,7 +729,7 @@
         <v>4.6361</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.567</v>
       </c>
       <c r="D7" t="n">
         <v>1.4515</v>
@@ -775,7 +775,7 @@
         <v>4.5527</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.5208</v>
       </c>
       <c r="D8" t="n">
         <v>1.4178</v>
@@ -821,7 +821,7 @@
         <v>4.2656</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.3619</v>
       </c>
       <c r="D9" t="n">
         <v>1.3018</v>
@@ -867,7 +867,7 @@
         <v>3.6754</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.0351</v>
       </c>
       <c r="D10" t="n">
         <v>1.0634</v>
@@ -913,7 +913,7 @@
         <v>3.0997</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1.7163</v>
       </c>
       <c r="D11" t="n">
         <v>0.8308</v>
@@ -959,7 +959,7 @@
         <v>3.0308</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.6781</v>
       </c>
       <c r="D12" t="n">
         <v>0.803</v>
@@ -1005,7 +1005,7 @@
         <v>2.7047</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.4976</v>
       </c>
       <c r="D13" t="n">
         <v>0.6713</v>
@@ -1051,7 +1051,7 @@
         <v>2.6082</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.4442</v>
       </c>
       <c r="D14" t="n">
         <v>0.6323</v>
@@ -1097,7 +1097,7 @@
         <v>2.5307</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.4012</v>
       </c>
       <c r="D15" t="n">
         <v>0.601</v>
@@ -1143,7 +1143,7 @@
         <v>2.5117</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.3907</v>
       </c>
       <c r="D16" t="n">
         <v>0.5933</v>
@@ -1189,7 +1189,7 @@
         <v>2.3922</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.3246</v>
       </c>
       <c r="D17" t="n">
         <v>0.545</v>
@@ -1235,7 +1235,7 @@
         <v>2.3196</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.2844</v>
       </c>
       <c r="D18" t="n">
         <v>0.5157</v>
@@ -1281,7 +1281,7 @@
         <v>2.2682</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.2559</v>
       </c>
       <c r="D19" t="n">
         <v>0.4949</v>
@@ -1327,7 +1327,7 @@
         <v>2.2174</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.2278</v>
       </c>
       <c r="D20" t="n">
         <v>0.4744</v>
@@ -1373,7 +1373,7 @@
         <v>2.1512</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.1911</v>
       </c>
       <c r="D21" t="n">
         <v>0.4477</v>
@@ -1419,7 +1419,7 @@
         <v>2.025</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.1212</v>
       </c>
       <c r="D22" t="n">
         <v>0.3967</v>
@@ -1465,7 +1465,7 @@
         <v>1.9636</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.0872</v>
       </c>
       <c r="D23" t="n">
         <v>0.3719</v>
@@ -1511,7 +1511,7 @@
         <v>1.9588</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.0846</v>
       </c>
       <c r="D24" t="n">
         <v>0.3699</v>
@@ -1557,7 +1557,7 @@
         <v>1.9023</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0533</v>
       </c>
       <c r="D25" t="n">
         <v>0.3471</v>
@@ -1603,7 +1603,7 @@
         <v>1.7901</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9912</v>
       </c>
       <c r="D26" t="n">
         <v>0.3018</v>
@@ -1649,7 +1649,7 @@
         <v>1.7612</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.9752</v>
       </c>
       <c r="D27" t="n">
         <v>0.2901</v>
@@ -1695,7 +1695,7 @@
         <v>1.6771</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.9286</v>
       </c>
       <c r="D28" t="n">
         <v>0.2561</v>
@@ -1741,7 +1741,7 @@
         <v>1.6582</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.9181</v>
       </c>
       <c r="D29" t="n">
         <v>0.2485</v>
@@ -1787,7 +1787,7 @@
         <v>1.6364</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.9061</v>
       </c>
       <c r="D30" t="n">
         <v>0.2397</v>
@@ -1833,7 +1833,7 @@
         <v>1.5461</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.8561</v>
       </c>
       <c r="D31" t="n">
         <v>0.2032</v>
@@ -1879,7 +1879,7 @@
         <v>1.3583</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.7521</v>
       </c>
       <c r="D32" t="n">
         <v>0.1274</v>
@@ -1925,7 +1925,7 @@
         <v>1.3123</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7266</v>
       </c>
       <c r="D33" t="n">
         <v>0.1088</v>
@@ -1971,7 +1971,7 @@
         <v>1.2827</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="D34" t="n">
         <v>0.0968</v>
@@ -2017,7 +2017,7 @@
         <v>1.2276</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.6797</v>
       </c>
       <c r="D35" t="n">
         <v>0.0746</v>
@@ -2063,7 +2063,7 @@
         <v>1.2028</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="D36" t="n">
         <v>0.0645</v>
@@ -2109,7 +2109,7 @@
         <v>1.1052</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="D37" t="n">
         <v>0.0251</v>
@@ -2155,7 +2155,7 @@
         <v>1.0823</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="D38" t="n">
         <v>0.0159</v>
@@ -2201,7 +2201,7 @@
         <v>1.0633</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.5887</v>
       </c>
       <c r="D39" t="n">
         <v>0.008200000000000001</v>
@@ -2247,7 +2247,7 @@
         <v>0.9314</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.5157</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0451</v>
@@ -2293,7 +2293,7 @@
         <v>0.851</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4712</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0776</v>
@@ -2339,7 +2339,7 @@
         <v>0.7985</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.4421</v>
       </c>
       <c r="D42" t="n">
         <v>-0.0988</v>
@@ -2385,7 +2385,7 @@
         <v>0.7927</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.4389</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1011</v>
@@ -2431,7 +2431,7 @@
         <v>0.7554999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.4183</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1162</v>
@@ -2477,7 +2477,7 @@
         <v>0.5074</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2809</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2164</v>
@@ -2523,7 +2523,7 @@
         <v>0.3822</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2116</v>
       </c>
       <c r="D46" t="n">
         <v>-0.267</v>
@@ -2569,7 +2569,7 @@
         <v>0.3818</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2114</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2671</v>
@@ -2615,7 +2615,7 @@
         <v>0.3617</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2003</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2752</v>
@@ -2661,7 +2661,7 @@
         <v>0.2692</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1491</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3126</v>
@@ -2707,7 +2707,7 @@
         <v>0.2198</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1217</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3326</v>
@@ -2753,7 +2753,7 @@
         <v>0.1885</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1044</v>
       </c>
       <c r="D51" t="n">
         <v>-0.3452</v>
@@ -2799,7 +2799,7 @@
         <v>0.101</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.0559</v>
       </c>
       <c r="D52" t="n">
         <v>-0.3806</v>
@@ -2845,7 +2845,7 @@
         <v>0.0973</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0539</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3821</v>
@@ -2891,7 +2891,7 @@
         <v>0.0607</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="D54" t="n">
         <v>-0.3968</v>
@@ -2937,7 +2937,7 @@
         <v>0.055</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0305</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3991</v>
@@ -2983,7 +2983,7 @@
         <v>0.008500000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.0047</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4179</v>
@@ -3029,7 +3029,7 @@
         <v>-0.2619</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.145</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5272</v>
@@ -3075,7 +3075,7 @@
         <v>-0.5259</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2912</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6338</v>
@@ -3121,7 +3121,7 @@
         <v>-0.6534</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.3618</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6853</v>
@@ -3167,7 +3167,7 @@
         <v>-0.7723</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.4276</v>
       </c>
       <c r="D60" t="n">
         <v>-0.7334000000000001</v>
@@ -3213,7 +3213,7 @@
         <v>-0.7736</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.4283</v>
       </c>
       <c r="D61" t="n">
         <v>-0.7339</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7897999999999999</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.4373</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7403999999999999</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7911</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.438</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7409</v>
@@ -3351,7 +3351,7 @@
         <v>-0.7947</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.44</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7423999999999999</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8115</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4493</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7492</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9242</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.5117</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7947</v>
@@ -3489,7 +3489,7 @@
         <v>-0.948</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.5249</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8043</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9527</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5275</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8062</v>
@@ -3581,7 +3581,7 @@
         <v>-0.9669</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.5354</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8120000000000001</v>
@@ -3627,7 +3627,7 @@
         <v>-0.9931</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8226</v>
@@ -3673,7 +3673,7 @@
         <v>-0.9987</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.553</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8248</v>
@@ -3719,7 +3719,7 @@
         <v>-1.025</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.5675</v>
       </c>
       <c r="D72" t="n">
         <v>-0.8354</v>
@@ -3765,7 +3765,7 @@
         <v>-1.1637</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.6443</v>
       </c>
       <c r="D73" t="n">
         <v>-0.8915</v>
@@ -3811,7 +3811,7 @@
         <v>-1.2612</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.6983</v>
       </c>
       <c r="D74" t="n">
         <v>-0.9308999999999999</v>
@@ -3857,7 +3857,7 @@
         <v>-1.2976</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.7185</v>
       </c>
       <c r="D75" t="n">
         <v>-0.9456</v>
@@ -3903,7 +3903,7 @@
         <v>-1.8993</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0516</v>
       </c>
       <c r="D76" t="n">
         <v>-1.1886</v>
@@ -3949,7 +3949,7 @@
         <v>-2.0786</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1509</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2611</v>
@@ -3995,7 +3995,7 @@
         <v>-2.193</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.2143</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3073</v>
@@ -4041,7 +4041,7 @@
         <v>-3.3497</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.8547</v>
       </c>
       <c r="D79" t="n">
         <v>-1.7746</v>
@@ -4087,7 +4087,7 @@
         <v>-3.4857</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.93</v>
       </c>
       <c r="D80" t="n">
         <v>-1.8295</v>
@@ -4133,7 +4133,7 @@
         <v>-5.0287</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.7844</v>
       </c>
       <c r="D81" t="n">
         <v>-2.4528</v>

--- a/database/event/7524/event_7524_evp_summary.xlsx
+++ b/database/event/7524/event_7524_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.6241</v>
+        <v>10.9799</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8825</v>
+        <v>6.0795</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8705</v>
+        <v>3.9305</v>
       </c>
       <c r="E2" t="n">
-        <v>10.6241</v>
+        <v>10.9799</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9597</v>
+        <v>4.3155</v>
       </c>
       <c r="G2" t="n">
         <v>6.6644</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9597</v>
+        <v>4.4636</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9597</v>
+        <v>4.4636</v>
       </c>
       <c r="J2" t="n">
         <v>8.2926</v>
@@ -529,7 +529,7 @@
         <v>167</v>
       </c>
       <c r="M2" t="n">
-        <v>12.2523</v>
+        <v>12.7562</v>
       </c>
       <c r="N2" t="n">
         <v>293</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.699</v>
+        <v>7.917</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2629</v>
+        <v>4.3836</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6889</v>
+        <v>2.7102</v>
       </c>
       <c r="E3" t="n">
-        <v>7.699</v>
+        <v>7.917</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1186</v>
+        <v>2.3366</v>
       </c>
       <c r="G3" t="n">
         <v>5.5805</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1186</v>
+        <v>2.3366</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1186</v>
+        <v>2.3366</v>
       </c>
       <c r="J3" t="n">
         <v>5.5805</v>
@@ -575,7 +575,7 @@
         <v>173</v>
       </c>
       <c r="M3" t="n">
-        <v>7.6991</v>
+        <v>7.9171</v>
       </c>
       <c r="N3" t="n">
         <v>337</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5767</v>
+        <v>6.1843</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0878</v>
+        <v>3.4242</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8315</v>
+        <v>2.0199</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5767</v>
+        <v>6.1843</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7449</v>
+        <v>4.3526</v>
       </c>
       <c r="G4" t="n">
         <v>1.8318</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7449</v>
+        <v>4.5218</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7449</v>
+        <v>4.5218</v>
       </c>
       <c r="J4" t="n">
         <v>1.8318</v>
@@ -621,7 +621,7 @@
         <v>119</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5767</v>
+        <v>6.3536</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4387</v>
+        <v>5.8878</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0114</v>
+        <v>3.2601</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7758</v>
+        <v>1.9018</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4387</v>
+        <v>5.8878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7149</v>
+        <v>1.164</v>
       </c>
       <c r="G5" t="n">
         <v>4.7238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7149</v>
+        <v>1.164</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7149</v>
+        <v>1.164</v>
       </c>
       <c r="J5" t="n">
         <v>4.7238</v>
@@ -667,7 +667,7 @@
         <v>167</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4387</v>
+        <v>5.887799999999999</v>
       </c>
       <c r="N5" t="n">
         <v>293</v>
@@ -676,369 +676,369 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1487</v>
+        <v>5.7018</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8508</v>
+        <v>3.1571</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6586</v>
+        <v>1.8277</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1487</v>
+        <v>5.7018</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2936</v>
+        <v>4.3798</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8551</v>
+        <v>1.322</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2936</v>
+        <v>4.5645</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2936</v>
+        <v>4.5645</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8551</v>
+        <v>1.322</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="L6" t="n">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1487</v>
+        <v>5.8865</v>
       </c>
       <c r="N6" t="n">
-        <v>293</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6361</v>
+        <v>5.6196</v>
       </c>
       <c r="C7" t="n">
-        <v>2.567</v>
+        <v>3.1116</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4515</v>
+        <v>1.7949</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6361</v>
+        <v>5.6196</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3141</v>
+        <v>2.7646</v>
       </c>
       <c r="G7" t="n">
-        <v>1.322</v>
+        <v>2.8551</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3141</v>
+        <v>2.7646</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3141</v>
+        <v>2.7646</v>
       </c>
       <c r="J7" t="n">
-        <v>1.322</v>
+        <v>2.8551</v>
       </c>
       <c r="K7" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6361</v>
+        <v>5.6197</v>
       </c>
       <c r="N7" t="n">
-        <v>143</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5527</v>
+        <v>5.1963</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5208</v>
+        <v>2.8772</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4178</v>
+        <v>1.6263</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5527</v>
+        <v>5.1963</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2914</v>
+        <v>3.6305</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2613</v>
+        <v>1.5658</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4258</v>
+        <v>3.6305</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4671</v>
+        <v>3.6305</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2613</v>
+        <v>1.5658</v>
       </c>
       <c r="K8" t="n">
-        <v>246</v>
+        <v>95</v>
       </c>
       <c r="L8" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="M8" t="n">
-        <v>4.728400000000001</v>
+        <v>5.1963</v>
       </c>
       <c r="N8" t="n">
-        <v>316</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2656</v>
+        <v>4.9761</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3619</v>
+        <v>2.7553</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3018</v>
+        <v>1.5386</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2656</v>
+        <v>4.9761</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6997</v>
+        <v>4.7148</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5658</v>
+        <v>0.2613</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6997</v>
+        <v>5.0898</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6997</v>
+        <v>5.1758</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5658</v>
+        <v>0.2613</v>
       </c>
       <c r="K9" t="n">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="L9" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2655</v>
+        <v>5.4371</v>
       </c>
       <c r="N9" t="n">
-        <v>214</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6754</v>
+        <v>4.0006</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0351</v>
+        <v>2.2151</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0634</v>
+        <v>1.1499</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6754</v>
+        <v>4.0006</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6754</v>
+        <v>2.5766</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.424</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6754</v>
+        <v>2.5766</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6754</v>
+        <v>2.5983</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.424</v>
       </c>
       <c r="K10" t="n">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6754</v>
+        <v>4.0223</v>
       </c>
       <c r="N10" t="n">
-        <v>204</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0997</v>
+        <v>3.6754</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7163</v>
+        <v>2.0351</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8308</v>
+        <v>1.0204</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0997</v>
+        <v>3.6754</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6757</v>
+        <v>3.6754</v>
       </c>
       <c r="G11" t="n">
-        <v>1.424</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6757</v>
+        <v>3.6754</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6835</v>
+        <v>3.6754</v>
       </c>
       <c r="J11" t="n">
-        <v>1.424</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="L11" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1075</v>
+        <v>3.6754</v>
       </c>
       <c r="N11" t="n">
-        <v>265</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0308</v>
+        <v>3.6352</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6781</v>
+        <v>2.0128</v>
       </c>
       <c r="D12" t="n">
-        <v>0.803</v>
+        <v>1.0044</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0308</v>
+        <v>3.6352</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3843</v>
+        <v>1.3304</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3535</v>
+        <v>2.3048</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3843</v>
+        <v>1.3304</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3843</v>
+        <v>1.3304</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3535</v>
+        <v>2.3048</v>
       </c>
       <c r="K12" t="n">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="L12" t="n">
-        <v>46</v>
+        <v>173</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0308</v>
+        <v>3.6352</v>
       </c>
       <c r="N12" t="n">
-        <v>170</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7047</v>
+        <v>3.0335</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4976</v>
+        <v>1.6796</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6713</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7047</v>
+        <v>3.0335</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3999</v>
+        <v>3.387</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3048</v>
+        <v>-0.3535</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3999</v>
+        <v>3.387</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3999</v>
+        <v>3.387</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3048</v>
+        <v>-0.3535</v>
       </c>
       <c r="K13" t="n">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="L13" t="n">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7047</v>
+        <v>3.0335</v>
       </c>
       <c r="N13" t="n">
-        <v>337</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6082</v>
+        <v>2.7878</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4442</v>
+        <v>1.5436</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6323</v>
+        <v>0.6667</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6082</v>
+        <v>2.7878</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9669</v>
+        <v>3.1465</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3587</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9669</v>
+        <v>3.1465</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9669</v>
+        <v>3.1465</v>
       </c>
       <c r="J14" t="n">
         <v>-0.3587</v>
@@ -1081,7 +1081,7 @@
         <v>46</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6082</v>
+        <v>2.7878</v>
       </c>
       <c r="N14" t="n">
         <v>170</v>
@@ -1090,127 +1090,127 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5307</v>
+        <v>2.6452</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4012</v>
+        <v>1.4646</v>
       </c>
       <c r="D15" t="n">
-        <v>0.601</v>
+        <v>0.6099</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5307</v>
+        <v>2.6452</v>
       </c>
       <c r="F15" t="n">
-        <v>2.024</v>
+        <v>2.1576</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5067</v>
+        <v>0.4876</v>
       </c>
       <c r="H15" t="n">
-        <v>2.024</v>
+        <v>2.1576</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0334</v>
+        <v>2.1941</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5067</v>
+        <v>0.4876</v>
       </c>
       <c r="K15" t="n">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="L15" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5401</v>
+        <v>2.6817</v>
       </c>
       <c r="N15" t="n">
-        <v>265</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5117</v>
+        <v>2.5636</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3907</v>
+        <v>1.4195</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5933</v>
+        <v>0.5774</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5117</v>
+        <v>2.5636</v>
       </c>
       <c r="F16" t="n">
-        <v>2.131</v>
+        <v>1.5342</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3807</v>
+        <v>1.0294</v>
       </c>
       <c r="H16" t="n">
-        <v>2.131</v>
+        <v>1.5342</v>
       </c>
       <c r="I16" t="n">
-        <v>2.131</v>
+        <v>1.5342</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3807</v>
+        <v>1.0294</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="M16" t="n">
-        <v>2.5117</v>
+        <v>2.5636</v>
       </c>
       <c r="N16" t="n">
-        <v>143</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3922</v>
+        <v>2.5341</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3246</v>
+        <v>1.4031</v>
       </c>
       <c r="D17" t="n">
-        <v>0.545</v>
+        <v>0.5657</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3922</v>
+        <v>2.5341</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3729</v>
+        <v>2.0274</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0193</v>
+        <v>0.5067</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3729</v>
+        <v>2.0274</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3839</v>
+        <v>2.0444</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0193</v>
+        <v>0.5067</v>
       </c>
       <c r="K17" t="n">
         <v>156</v>
@@ -1219,7 +1219,7 @@
         <v>109</v>
       </c>
       <c r="M17" t="n">
-        <v>2.4032</v>
+        <v>2.5511</v>
       </c>
       <c r="N17" t="n">
         <v>265</v>
@@ -1228,354 +1228,354 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3196</v>
+        <v>2.5117</v>
       </c>
       <c r="C18" t="n">
-        <v>1.2844</v>
+        <v>1.3907</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5157</v>
+        <v>0.5568</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3196</v>
+        <v>2.5117</v>
       </c>
       <c r="F18" t="n">
-        <v>0.794</v>
+        <v>2.131</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5256</v>
+        <v>0.3807</v>
       </c>
       <c r="H18" t="n">
-        <v>0.794</v>
+        <v>2.131</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7977</v>
+        <v>2.131</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5256</v>
+        <v>0.3807</v>
       </c>
       <c r="K18" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="L18" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3233</v>
+        <v>2.5117</v>
       </c>
       <c r="N18" t="n">
-        <v>265</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2682</v>
+        <v>2.489</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2559</v>
+        <v>1.3782</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4949</v>
+        <v>0.5477</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2682</v>
+        <v>2.489</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2682</v>
+        <v>2.1402</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3488</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2682</v>
+        <v>2.1402</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2682</v>
+        <v>2.1402</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3488</v>
       </c>
       <c r="K19" t="n">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2682</v>
+        <v>2.489</v>
       </c>
       <c r="N19" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2174</v>
+        <v>2.3833</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2278</v>
+        <v>1.3196</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4744</v>
+        <v>0.5056</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2174</v>
+        <v>2.3833</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2174</v>
+        <v>2.364</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0193</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2174</v>
+        <v>2.364</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2174</v>
+        <v>2.3839</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.0193</v>
       </c>
       <c r="K20" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2174</v>
+        <v>2.4032</v>
       </c>
       <c r="N20" t="n">
-        <v>159</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1512</v>
+        <v>2.3677</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1911</v>
+        <v>1.311</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4477</v>
+        <v>0.4994</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1512</v>
+        <v>2.3677</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8024</v>
+        <v>2.3677</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3488</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8024</v>
+        <v>2.3677</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8024</v>
+        <v>2.3677</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3488</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>83</v>
+        <v>159</v>
       </c>
       <c r="L21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1512</v>
+        <v>2.3677</v>
       </c>
       <c r="N21" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.025</v>
+        <v>2.3166</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1212</v>
+        <v>1.2827</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3967</v>
+        <v>0.479</v>
       </c>
       <c r="E22" t="n">
-        <v>2.025</v>
+        <v>2.3166</v>
       </c>
       <c r="F22" t="n">
-        <v>2.025</v>
+        <v>0.791</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.5256</v>
       </c>
       <c r="H22" t="n">
-        <v>2.025</v>
+        <v>0.791</v>
       </c>
       <c r="I22" t="n">
-        <v>2.025</v>
+        <v>0.7977</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.5256</v>
       </c>
       <c r="K22" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M22" t="n">
-        <v>2.025</v>
+        <v>2.3233</v>
       </c>
       <c r="N22" t="n">
-        <v>179</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9636</v>
+        <v>2.2897</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0872</v>
+        <v>1.2678</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3719</v>
+        <v>0.4683</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9636</v>
+        <v>2.2897</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9636</v>
+        <v>2.2897</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9636</v>
+        <v>2.2897</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9636</v>
+        <v>2.2897</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.9636</v>
+        <v>2.2897</v>
       </c>
       <c r="N23" t="n">
-        <v>204</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9588</v>
+        <v>2.2682</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0846</v>
+        <v>1.2559</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3699</v>
+        <v>0.4597</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9588</v>
+        <v>2.2682</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9294</v>
+        <v>2.2682</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0294</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9294</v>
+        <v>2.2682</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9294</v>
+        <v>2.2682</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0294</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L24" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.9588</v>
+        <v>2.2682</v>
       </c>
       <c r="N24" t="n">
-        <v>337</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.9023</v>
+        <v>2.1018</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0533</v>
+        <v>1.1638</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3471</v>
+        <v>0.3934</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9023</v>
+        <v>2.1018</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9023</v>
+        <v>2.1018</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9023</v>
+        <v>2.1018</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9023</v>
+        <v>2.1018</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.9023</v>
+        <v>2.1018</v>
       </c>
       <c r="N25" t="n">
         <v>159</v>
@@ -1596,127 +1596,127 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7901</v>
+        <v>2.025</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9912</v>
+        <v>1.1212</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3018</v>
+        <v>0.3628</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7901</v>
+        <v>2.025</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2296</v>
+        <v>2.025</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4395</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2296</v>
+        <v>2.025</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2296</v>
+        <v>2.025</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4395</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="L26" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7901</v>
+        <v>2.025</v>
       </c>
       <c r="N26" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7612</v>
+        <v>1.9636</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9752</v>
+        <v>1.0872</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2901</v>
+        <v>0.3384</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7612</v>
+        <v>1.9636</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2166</v>
+        <v>1.9636</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5446</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.2166</v>
+        <v>1.9636</v>
       </c>
       <c r="I27" t="n">
-        <v>1.228</v>
+        <v>1.9636</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5446</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7726</v>
+        <v>1.9636</v>
       </c>
       <c r="N27" t="n">
-        <v>316</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6771</v>
+        <v>1.8489</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9286</v>
+        <v>1.0237</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2561</v>
+        <v>0.2927</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6771</v>
+        <v>1.8489</v>
       </c>
       <c r="F28" t="n">
-        <v>0.356</v>
+        <v>2.8489</v>
       </c>
       <c r="G28" t="n">
-        <v>1.3211</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.356</v>
+        <v>2.8489</v>
       </c>
       <c r="I28" t="n">
-        <v>0.356</v>
+        <v>2.8489</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3211</v>
+        <v>-1</v>
       </c>
       <c r="K28" t="n">
         <v>128</v>
@@ -1725,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6771</v>
+        <v>1.8489</v>
       </c>
       <c r="N28" t="n">
         <v>180</v>
@@ -1734,277 +1734,277 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.6582</v>
+        <v>1.812</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9181</v>
+        <v>1.0033</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2485</v>
+        <v>0.278</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6582</v>
+        <v>1.812</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.187</v>
+        <v>1.812</v>
       </c>
       <c r="G29" t="n">
-        <v>3.8452</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-2.187</v>
+        <v>1.812</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.187</v>
+        <v>1.812</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8452</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="L29" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.6582</v>
+        <v>1.812</v>
       </c>
       <c r="N29" t="n">
-        <v>337</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.6364</v>
+        <v>1.7901</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9061</v>
+        <v>0.9912</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2397</v>
+        <v>0.2693</v>
       </c>
       <c r="E30" t="n">
-        <v>1.6364</v>
+        <v>1.7901</v>
       </c>
       <c r="F30" t="n">
-        <v>1.6364</v>
+        <v>2.2296</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4395</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6364</v>
+        <v>2.2296</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6364</v>
+        <v>2.2296</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4395</v>
       </c>
       <c r="K30" t="n">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.6364</v>
+        <v>1.7901</v>
       </c>
       <c r="N30" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.5461</v>
+        <v>1.7522</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8561</v>
+        <v>0.9702</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2032</v>
+        <v>0.2542</v>
       </c>
       <c r="E31" t="n">
-        <v>1.5461</v>
+        <v>1.7522</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5461</v>
+        <v>1.2076</v>
       </c>
       <c r="G31" t="n">
-        <v>-1</v>
+        <v>0.5446</v>
       </c>
       <c r="H31" t="n">
-        <v>2.5461</v>
+        <v>1.2076</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5461</v>
+        <v>1.228</v>
       </c>
       <c r="J31" t="n">
-        <v>-1</v>
+        <v>0.5446</v>
       </c>
       <c r="K31" t="n">
-        <v>128</v>
+        <v>246</v>
       </c>
       <c r="L31" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="M31" t="n">
-        <v>1.5461</v>
+        <v>1.7726</v>
       </c>
       <c r="N31" t="n">
-        <v>180</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3583</v>
+        <v>1.6771</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7521</v>
+        <v>0.9286</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1274</v>
+        <v>0.2242</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3583</v>
+        <v>1.6771</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3583</v>
+        <v>0.356</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.3211</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3583</v>
+        <v>0.356</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3583</v>
+        <v>0.356</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.3211</v>
       </c>
       <c r="K32" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3583</v>
+        <v>1.6771</v>
       </c>
       <c r="N32" t="n">
-        <v>117</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3123</v>
+        <v>1.6582</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7266</v>
+        <v>0.9181</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1088</v>
+        <v>0.2167</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3123</v>
+        <v>1.6582</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9504</v>
+        <v>-2.187</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3619</v>
+        <v>3.8452</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9504</v>
+        <v>-2.187</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9548</v>
+        <v>-2.187</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3619</v>
+        <v>3.8452</v>
       </c>
       <c r="K33" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="L33" t="n">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3167</v>
+        <v>1.6582</v>
       </c>
       <c r="N33" t="n">
-        <v>265</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2827</v>
+        <v>1.3087</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.7246</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0968</v>
+        <v>0.0775</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2827</v>
+        <v>1.3087</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7951</v>
+        <v>0.9468</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4876</v>
+        <v>0.3619</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7951</v>
+        <v>0.9468</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8025</v>
+        <v>0.9548</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4876</v>
+        <v>0.3619</v>
       </c>
       <c r="K34" t="n">
-        <v>246</v>
+        <v>156</v>
       </c>
       <c r="L34" t="n">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2901</v>
+        <v>1.3167</v>
       </c>
       <c r="N34" t="n">
-        <v>316</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2276</v>
+        <v>1.2699</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6797</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0746</v>
+        <v>0.062</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2276</v>
+        <v>1.2699</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2276</v>
+        <v>1.2699</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2276</v>
+        <v>1.2699</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2276</v>
+        <v>1.2699</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2276</v>
+        <v>1.2699</v>
       </c>
       <c r="N35" t="n">
         <v>117</v>
@@ -2066,7 +2066,7 @@
         <v>0.666</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0645</v>
+        <v>0.0353</v>
       </c>
       <c r="E36" t="n">
         <v>1.2028</v>
@@ -2102,1642 +2102,1642 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.1052</v>
+        <v>1.199</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6119</v>
+        <v>0.6639</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0251</v>
+        <v>0.0338</v>
       </c>
       <c r="E37" t="n">
-        <v>1.1052</v>
+        <v>1.199</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5441</v>
+        <v>2.4394</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.4389</v>
+        <v>-1.2404</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5441</v>
+        <v>2.4394</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5441</v>
+        <v>2.4394</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4389</v>
+        <v>-1.2404</v>
       </c>
       <c r="K37" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="L37" t="n">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1052</v>
+        <v>1.199</v>
       </c>
       <c r="N37" t="n">
-        <v>214</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.0823</v>
+        <v>1.1974</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0159</v>
+        <v>0.0331</v>
       </c>
       <c r="E38" t="n">
-        <v>1.0823</v>
+        <v>1.1974</v>
       </c>
       <c r="F38" t="n">
-        <v>1.0823</v>
+        <v>2.1974</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.0823</v>
+        <v>2.1974</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0823</v>
+        <v>2.1974</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K38" t="n">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M38" t="n">
-        <v>1.0823</v>
+        <v>1.1974</v>
       </c>
       <c r="N38" t="n">
-        <v>179</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.0633</v>
+        <v>1.1128</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5887</v>
+        <v>0.6162</v>
       </c>
       <c r="D39" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>1.0633</v>
+        <v>1.1128</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5959</v>
+        <v>1.1128</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4674</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5959</v>
+        <v>1.1128</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5959</v>
+        <v>1.1128</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4674</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="L39" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.0633</v>
+        <v>1.1128</v>
       </c>
       <c r="N39" t="n">
-        <v>170</v>
+        <v>204</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9314</v>
+        <v>1.1052</v>
       </c>
       <c r="C40" t="n">
-        <v>0.5157</v>
+        <v>0.6119</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0451</v>
+        <v>-0.0036</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9314</v>
+        <v>1.1052</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9314</v>
+        <v>1.5441</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.4389</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9314</v>
+        <v>1.5441</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9314</v>
+        <v>1.5441</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.4389</v>
       </c>
       <c r="K40" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9314</v>
+        <v>1.1052</v>
       </c>
       <c r="N40" t="n">
-        <v>104</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.851</v>
+        <v>1.0823</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4712</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0776</v>
+        <v>-0.0127</v>
       </c>
       <c r="E41" t="n">
-        <v>0.851</v>
+        <v>1.0823</v>
       </c>
       <c r="F41" t="n">
-        <v>0.851</v>
+        <v>1.0823</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.851</v>
+        <v>1.0823</v>
       </c>
       <c r="I41" t="n">
-        <v>0.851</v>
+        <v>1.0823</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.851</v>
+        <v>1.0823</v>
       </c>
       <c r="N41" t="n">
-        <v>204</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7985</v>
+        <v>1.0633</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4421</v>
+        <v>0.5887</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0988</v>
+        <v>-0.0203</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7985</v>
+        <v>1.0633</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5864</v>
+        <v>0.5959</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.7879</v>
+        <v>0.4674</v>
       </c>
       <c r="H42" t="n">
-        <v>1.5864</v>
+        <v>0.5959</v>
       </c>
       <c r="I42" t="n">
-        <v>1.5864</v>
+        <v>0.5959</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.7879</v>
+        <v>0.4674</v>
       </c>
       <c r="K42" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="L42" t="n">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7985</v>
+        <v>1.0633</v>
       </c>
       <c r="N42" t="n">
-        <v>214</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7927</v>
+        <v>0.9314</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4389</v>
+        <v>0.5157</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1011</v>
+        <v>-0.0728</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7927</v>
+        <v>0.9314</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4717</v>
+        <v>0.9314</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.679</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.4717</v>
+        <v>0.9314</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4854</v>
+        <v>0.9314</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.679</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="L43" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8064</v>
+        <v>0.9314</v>
       </c>
       <c r="N43" t="n">
-        <v>316</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7985</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4183</v>
+        <v>0.4421</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1162</v>
+        <v>-0.1258</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7985</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7555</v>
+        <v>1.5864</v>
       </c>
       <c r="G44" t="n">
-        <v>-1</v>
+        <v>-0.7879</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7555</v>
+        <v>1.5864</v>
       </c>
       <c r="I44" t="n">
-        <v>1.7555</v>
+        <v>1.5864</v>
       </c>
       <c r="J44" t="n">
-        <v>-1</v>
+        <v>-0.7879</v>
       </c>
       <c r="K44" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="L44" t="n">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7985</v>
       </c>
       <c r="N44" t="n">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5074</v>
+        <v>0.7817</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2809</v>
+        <v>0.4328</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2164</v>
+        <v>-0.1325</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5074</v>
+        <v>0.7817</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5074</v>
+        <v>1.4607</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.679</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5074</v>
+        <v>1.4607</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5074</v>
+        <v>1.4854</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.679</v>
       </c>
       <c r="K45" t="n">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5074</v>
+        <v>0.8064</v>
       </c>
       <c r="N45" t="n">
-        <v>104</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3822</v>
+        <v>0.742</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2116</v>
+        <v>0.4108</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.267</v>
+        <v>-0.1483</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3822</v>
+        <v>0.742</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6226</v>
+        <v>0.742</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.2404</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.6226</v>
+        <v>0.742</v>
       </c>
       <c r="I46" t="n">
-        <v>1.6226</v>
+        <v>0.742</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.2404</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="L46" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.3822000000000001</v>
+        <v>0.742</v>
       </c>
       <c r="N46" t="n">
-        <v>293</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3818</v>
+        <v>0.5074</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2114</v>
+        <v>0.2809</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2671</v>
+        <v>-0.2418</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3818</v>
+        <v>0.5074</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3818</v>
+        <v>0.5074</v>
       </c>
       <c r="G47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3818</v>
+        <v>0.5074</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3818</v>
+        <v>0.5074</v>
       </c>
       <c r="J47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="L47" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3817999999999999</v>
+        <v>0.5074</v>
       </c>
       <c r="N47" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3617</v>
+        <v>0.4644</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2003</v>
+        <v>0.2571</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2752</v>
+        <v>-0.2589</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3617</v>
+        <v>0.4644</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3617</v>
+        <v>0.2722</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.1922</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3617</v>
+        <v>0.2722</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3617</v>
+        <v>0.2722</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.1922</v>
       </c>
       <c r="K48" t="n">
-        <v>204</v>
+        <v>128</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3617</v>
+        <v>0.4644</v>
       </c>
       <c r="N48" t="n">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2692</v>
+        <v>0.3908</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1491</v>
+        <v>0.2164</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3126</v>
+        <v>-0.2882</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2692</v>
+        <v>0.3908</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2692</v>
+        <v>0.3908</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2692</v>
+        <v>0.3908</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2692</v>
+        <v>0.3908</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.2692</v>
+        <v>0.3908</v>
       </c>
       <c r="N49" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2198</v>
+        <v>0.3818</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1217</v>
+        <v>0.2114</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3326</v>
+        <v>-0.2918</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2198</v>
+        <v>0.3818</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2198</v>
+        <v>1.3818</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2198</v>
+        <v>1.3818</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2198</v>
+        <v>1.3818</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K50" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M50" t="n">
-        <v>0.2198</v>
+        <v>0.3817999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1885</v>
+        <v>0.2692</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1044</v>
+        <v>0.1491</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3452</v>
+        <v>-0.3367</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1885</v>
+        <v>0.2692</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0037</v>
+        <v>0.2692</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0037</v>
+        <v>0.2692</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.0037</v>
+        <v>0.2692</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="L51" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1885</v>
+        <v>0.2692</v>
       </c>
       <c r="N51" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.101</v>
+        <v>0.2198</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0559</v>
+        <v>0.1217</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3806</v>
+        <v>-0.3563</v>
       </c>
       <c r="E52" t="n">
-        <v>0.101</v>
+        <v>0.2198</v>
       </c>
       <c r="F52" t="n">
-        <v>0.101</v>
+        <v>0.2198</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.101</v>
+        <v>0.2198</v>
       </c>
       <c r="I52" t="n">
-        <v>0.101</v>
+        <v>0.2198</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.101</v>
+        <v>0.2198</v>
       </c>
       <c r="N52" t="n">
-        <v>204</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0973</v>
+        <v>0.1915</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0539</v>
+        <v>0.106</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3821</v>
+        <v>-0.3676</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0973</v>
+        <v>0.1915</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0973</v>
+        <v>0.1915</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0973</v>
+        <v>0.1915</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0973</v>
+        <v>0.1915</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0973</v>
+        <v>0.1915</v>
       </c>
       <c r="N53" t="n">
-        <v>148</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0607</v>
+        <v>0.1084</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0336</v>
+        <v>0.06</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3968</v>
+        <v>-0.4007</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0607</v>
+        <v>0.1084</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0607</v>
+        <v>0.1084</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0607</v>
+        <v>0.1084</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0607</v>
+        <v>0.1084</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0607</v>
+        <v>0.1084</v>
       </c>
       <c r="N54" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.055</v>
+        <v>0.0974</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0305</v>
+        <v>0.0539</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3991</v>
+        <v>-0.4051</v>
       </c>
       <c r="E55" t="n">
-        <v>0.055</v>
+        <v>0.0974</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4907</v>
+        <v>0.0974</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5457</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4907</v>
+        <v>0.0974</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4907</v>
+        <v>0.0974</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5457</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="L55" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.05499999999999994</v>
+        <v>0.0974</v>
       </c>
       <c r="N55" t="n">
-        <v>214</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0607</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0047</v>
+        <v>0.0336</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4179</v>
+        <v>-0.4197</v>
       </c>
       <c r="E56" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0607</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1932</v>
+        <v>0.0607</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.1847</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1932</v>
+        <v>0.0607</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1932</v>
+        <v>0.0607</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1847</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="L56" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.008500000000000008</v>
+        <v>0.0607</v>
       </c>
       <c r="N56" t="n">
-        <v>170</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2619</v>
+        <v>0.055</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.145</v>
+        <v>0.0305</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5272</v>
+        <v>-0.422</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2619</v>
+        <v>0.055</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.2619</v>
+        <v>-0.4907</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.5457</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.2619</v>
+        <v>-0.4907</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.2619</v>
+        <v>-0.4907</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.5457</v>
       </c>
       <c r="K57" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2619</v>
+        <v>0.05499999999999994</v>
       </c>
       <c r="N57" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5259</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2912</v>
+        <v>0.0047</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6338</v>
+        <v>-0.4405</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5259</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>0.396</v>
+        <v>0.1932</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.1847</v>
       </c>
       <c r="H58" t="n">
-        <v>0.396</v>
+        <v>0.1932</v>
       </c>
       <c r="I58" t="n">
-        <v>0.396</v>
+        <v>0.1932</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.1847</v>
       </c>
       <c r="K58" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L58" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5259</v>
+        <v>0.008500000000000008</v>
       </c>
       <c r="N58" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6534</v>
+        <v>-0.2619</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3618</v>
+        <v>-0.145</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6853</v>
+        <v>-0.5483</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6534</v>
+        <v>-0.2619</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6534</v>
+        <v>-0.2619</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6534</v>
+        <v>-0.2619</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6534</v>
+        <v>-0.2619</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6534</v>
+        <v>-0.2619</v>
       </c>
       <c r="N59" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.7723</v>
+        <v>-0.3841</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.4276</v>
+        <v>-0.2127</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.5969</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.7723</v>
+        <v>-0.3841</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.7723</v>
+        <v>-0.0615</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-0.3226</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.7723</v>
+        <v>-0.0615</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7723</v>
+        <v>-0.0615</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>-0.3226</v>
       </c>
       <c r="K60" t="n">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.7723</v>
+        <v>-0.3841</v>
       </c>
       <c r="N60" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7736</v>
+        <v>-0.5259</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4283</v>
+        <v>-0.2912</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7339</v>
+        <v>-0.6534</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7736</v>
+        <v>-0.5259</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7736</v>
+        <v>0.396</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7736</v>
+        <v>0.396</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7736</v>
+        <v>0.396</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7736</v>
+        <v>-0.5259</v>
       </c>
       <c r="N61" t="n">
-        <v>117</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4373</v>
+        <v>-0.3618</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7042</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.6534</v>
       </c>
       <c r="N62" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7911</v>
+        <v>-0.7659</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.438</v>
+        <v>-0.4241</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7409</v>
+        <v>-0.749</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7911</v>
+        <v>-0.7659</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7911</v>
+        <v>-0.7659</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7911</v>
+        <v>-0.7659</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7911</v>
+        <v>-0.7659</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7911</v>
+        <v>-0.7659</v>
       </c>
       <c r="N63" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7947</v>
+        <v>-0.7736</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.44</v>
+        <v>-0.4283</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.7521</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7947</v>
+        <v>-0.7736</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7947</v>
+        <v>-0.7736</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7947</v>
+        <v>-0.7736</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7947</v>
+        <v>-0.7736</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7947</v>
+        <v>-0.7736</v>
       </c>
       <c r="N64" t="n">
-        <v>179</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8115</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4493</v>
+        <v>-0.4373</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7492</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8115</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8115</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8115</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8115</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8115</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.9242</v>
+        <v>-0.7911</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5117</v>
+        <v>-0.438</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7947</v>
+        <v>-0.7591</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.9242</v>
+        <v>-0.7911</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9242</v>
+        <v>-0.7911</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9242</v>
+        <v>-0.7911</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9242</v>
+        <v>-0.7911</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.9242</v>
+        <v>-0.7911</v>
       </c>
       <c r="N66" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.948</v>
+        <v>-0.7947</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5249</v>
+        <v>-0.44</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8043</v>
+        <v>-0.7605</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.948</v>
+        <v>-0.7947</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.948</v>
+        <v>-0.7947</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.948</v>
+        <v>-0.7947</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.948</v>
+        <v>-0.7947</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.948</v>
+        <v>-0.7947</v>
       </c>
       <c r="N67" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9527</v>
+        <v>-0.9242</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5275</v>
+        <v>-0.5117</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8062</v>
+        <v>-0.8121</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9527</v>
+        <v>-0.9242</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9527</v>
+        <v>-0.9242</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9527</v>
+        <v>-0.9242</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.9527</v>
+        <v>-0.9242</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9527</v>
+        <v>-0.9242</v>
       </c>
       <c r="N68" t="n">
-        <v>117</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9669</v>
+        <v>-0.9298</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5354</v>
+        <v>-0.5148</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.8143</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9669</v>
+        <v>-0.9298</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6484</v>
+        <v>-0.9298</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.3185</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6484</v>
+        <v>-0.9298</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6545</v>
+        <v>-0.9298</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.3185</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="L69" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.973</v>
+        <v>-0.9298</v>
       </c>
       <c r="N69" t="n">
-        <v>316</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9931</v>
+        <v>-0.9527</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.5275</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8226</v>
+        <v>-0.8235</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9931</v>
+        <v>-0.9527</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9931</v>
+        <v>-0.9527</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9931</v>
+        <v>-0.9527</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9931</v>
+        <v>-0.9527</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9931</v>
+        <v>-0.9527</v>
       </c>
       <c r="N70" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9987</v>
+        <v>-0.9621</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.553</v>
+        <v>-0.5327</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8248</v>
+        <v>-0.8272</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9987</v>
+        <v>-0.9621</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9987</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.3185</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9987</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9987</v>
+        <v>-0.6545</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.3185</v>
       </c>
       <c r="K71" t="n">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9987</v>
+        <v>-0.973</v>
       </c>
       <c r="N71" t="n">
-        <v>104</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.025</v>
+        <v>-0.9931</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5675</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8354</v>
+        <v>-0.8396</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.025</v>
+        <v>-0.9931</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.025</v>
+        <v>-0.9931</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.025</v>
+        <v>-0.9931</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.025</v>
+        <v>-0.9931</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.025</v>
+        <v>-0.9931</v>
       </c>
       <c r="N72" t="n">
         <v>148</v>
@@ -3758,139 +3758,139 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1637</v>
+        <v>-0.9987</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6443</v>
+        <v>-0.553</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8915</v>
+        <v>-0.8418</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1637</v>
+        <v>-0.9987</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2521</v>
+        <v>-0.9987</v>
       </c>
       <c r="G73" t="n">
-        <v>0.08840000000000001</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2521</v>
+        <v>-0.9987</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2521</v>
+        <v>-0.9987</v>
       </c>
       <c r="J73" t="n">
-        <v>0.08840000000000001</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="L73" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1637</v>
+        <v>-0.9987</v>
       </c>
       <c r="N73" t="n">
-        <v>180</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.2612</v>
+        <v>-1.025</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6983</v>
+        <v>-0.5675</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.2612</v>
+        <v>-1.025</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.2612</v>
+        <v>-1.025</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.2612</v>
+        <v>-1.025</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2612</v>
+        <v>-1.025</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.2612</v>
+        <v>-1.025</v>
       </c>
       <c r="N74" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2976</v>
+        <v>-1.1637</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7185</v>
+        <v>-0.6443</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9456</v>
+        <v>-0.9075</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2976</v>
+        <v>-1.1637</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.975</v>
+        <v>-1.2521</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.3226</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.975</v>
+        <v>-1.2521</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.975</v>
+        <v>-1.2521</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.3226</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="L75" t="n">
-        <v>167</v>
+        <v>52</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.2976</v>
+        <v>-1.1637</v>
       </c>
       <c r="N75" t="n">
-        <v>293</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76">
@@ -3906,7 +3906,7 @@
         <v>-1.0516</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1886</v>
+        <v>-1.2006</v>
       </c>
       <c r="E76" t="n">
         <v>-1.8993</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1509</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2611</v>
+        <v>-1.272</v>
       </c>
       <c r="E77" t="n">
         <v>-2.0786</v>
@@ -3998,7 +3998,7 @@
         <v>-1.2143</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3073</v>
+        <v>-1.3176</v>
       </c>
       <c r="E78" t="n">
         <v>-2.193</v>
@@ -4044,7 +4044,7 @@
         <v>-1.8547</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7746</v>
+        <v>-1.7784</v>
       </c>
       <c r="E79" t="n">
         <v>-3.3497</v>
@@ -4090,7 +4090,7 @@
         <v>-1.93</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.8295</v>
+        <v>-1.8326</v>
       </c>
       <c r="E80" t="n">
         <v>-3.4857</v>
@@ -4136,7 +4136,7 @@
         <v>-2.7844</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.4528</v>
+        <v>-2.4473</v>
       </c>
       <c r="E81" t="n">
         <v>-5.0287</v>

--- a/database/event/7524/event_7524_evp_summary.xlsx
+++ b/database/event/7524/event_7524_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.1256</v>
+        <v>10.7665</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6065</v>
+        <v>5.9614</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9852</v>
+        <v>4.1953</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1256</v>
+        <v>10.7665</v>
       </c>
       <c r="F2" t="n">
         <v>3.9348</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4848</v>
+        <v>7.881</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1443</v>
+        <v>4.3637</v>
       </c>
       <c r="D3" t="n">
-        <v>2.783</v>
+        <v>2.9065</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4848</v>
+        <v>7.881</v>
       </c>
       <c r="F3" t="n">
         <v>2.5737</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9273</v>
+        <v>5.9797</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2819</v>
+        <v>3.3109</v>
       </c>
       <c r="D4" t="n">
-        <v>2.074</v>
+        <v>2.0572</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9273</v>
+        <v>5.9797</v>
       </c>
       <c r="F4" t="n">
         <v>1.531</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5227</v>
+        <v>5.5765</v>
       </c>
       <c r="C5" t="n">
-        <v>3.0579</v>
+        <v>3.0877</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8898</v>
+        <v>1.8771</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5227</v>
+        <v>5.5765</v>
       </c>
       <c r="F5" t="n">
         <v>2.4995</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.107</v>
+        <v>5.4301</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8277</v>
+        <v>3.0066</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7006</v>
+        <v>1.8117</v>
       </c>
       <c r="E6" t="n">
-        <v>5.107</v>
+        <v>5.4301</v>
       </c>
       <c r="F6" t="n">
         <v>3.5399</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5228</v>
+        <v>4.7633</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5043</v>
+        <v>2.6374</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4347</v>
+        <v>1.5138</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5228</v>
+        <v>4.7633</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2669</v>
+        <v>3.2606</v>
       </c>
       <c r="G7" t="n">
         <v>1.2559</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4253</v>
+        <v>4.4116</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4253</v>
+        <v>4.4116</v>
       </c>
       <c r="J7" t="n">
         <v>1.2559</v>
@@ -759,7 +759,7 @@
         <v>60</v>
       </c>
       <c r="M7" t="n">
-        <v>5.6812</v>
+        <v>5.6675</v>
       </c>
       <c r="N7" t="n">
         <v>143</v>
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.4549</v>
+        <v>4.4923</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4667</v>
+        <v>2.4874</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4038</v>
+        <v>1.3928</v>
       </c>
       <c r="E8" t="n">
-        <v>4.4549</v>
+        <v>4.4923</v>
       </c>
       <c r="F8" t="n">
         <v>1.8779</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4376</v>
+        <v>4.47</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4571</v>
+        <v>2.475</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3959</v>
+        <v>1.3828</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4376</v>
+        <v>4.47</v>
       </c>
       <c r="F9" t="n">
         <v>3.0224</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0591</v>
+        <v>4.2568</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2475</v>
+        <v>2.357</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2236</v>
+        <v>1.2876</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0591</v>
+        <v>4.2568</v>
       </c>
       <c r="F10" t="n">
         <v>3.654</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.9821</v>
+        <v>3.9265</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2049</v>
+        <v>2.1741</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1885</v>
+        <v>1.1401</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9821</v>
+        <v>3.9265</v>
       </c>
       <c r="F11" t="n">
         <v>2.4941</v>
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5112</v>
+        <v>3.5327</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9441</v>
+        <v>1.956</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9742</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5112</v>
+        <v>3.5327</v>
       </c>
       <c r="F12" t="n">
         <v>2.1014</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2177</v>
+        <v>3.3552</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7816</v>
+        <v>1.8578</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8406</v>
+        <v>0.8849</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2177</v>
+        <v>3.3552</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2177</v>
+        <v>3.2252</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3176</v>
+        <v>4.334</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3176</v>
+        <v>4.334</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.3176</v>
+        <v>4.334</v>
       </c>
       <c r="N13" t="n">
         <v>204</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1297</v>
+        <v>3.1705</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7329</v>
+        <v>1.7555</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8005</v>
+        <v>0.8024</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1297</v>
+        <v>3.1705</v>
       </c>
       <c r="F14" t="n">
         <v>2.2551</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0055</v>
+        <v>3.0721</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6641</v>
+        <v>1.701</v>
       </c>
       <c r="D15" t="n">
-        <v>0.744</v>
+        <v>0.7584</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0055</v>
+        <v>3.0721</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4162</v>
+        <v>3.1538</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5893</v>
+        <v>-0.1976</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5633</v>
+        <v>4.1777</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6971</v>
+        <v>4.1777</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5893</v>
+        <v>-0.1976</v>
       </c>
       <c r="K15" t="n">
-        <v>246</v>
+        <v>124</v>
       </c>
       <c r="L15" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2864</v>
+        <v>3.9801</v>
       </c>
       <c r="N15" t="n">
-        <v>316</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9562</v>
+        <v>3.0041</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6368</v>
+        <v>1.6634</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7215</v>
+        <v>0.728</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9562</v>
+        <v>3.0041</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1538</v>
+        <v>2.4162</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1976</v>
+        <v>0.5893</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1777</v>
+        <v>2.5633</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1777</v>
+        <v>2.6971</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1976</v>
+        <v>0.5893</v>
       </c>
       <c r="K16" t="n">
-        <v>124</v>
+        <v>246</v>
       </c>
       <c r="L16" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9801</v>
+        <v>3.2864</v>
       </c>
       <c r="N16" t="n">
-        <v>170</v>
+        <v>316</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8372</v>
+        <v>2.9137</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5709</v>
+        <v>1.6133</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6673</v>
+        <v>0.6877</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8372</v>
+        <v>2.9137</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4116</v>
+        <v>2.9109</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4256</v>
+        <v>-0.0752</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5532</v>
+        <v>3.6462</v>
       </c>
       <c r="I17" t="n">
-        <v>2.619</v>
+        <v>3.6462</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4256</v>
+        <v>-0.0752</v>
       </c>
       <c r="K17" t="n">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="L17" t="n">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0446</v>
+        <v>3.571</v>
       </c>
       <c r="N17" t="n">
-        <v>265</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.8357</v>
+        <v>2.8881</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5701</v>
+        <v>1.5991</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6667</v>
+        <v>0.6762</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8357</v>
+        <v>2.8881</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9109</v>
+        <v>2.4116</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0752</v>
+        <v>0.4256</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6462</v>
+        <v>2.5532</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6462</v>
+        <v>2.619</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0752</v>
+        <v>0.4256</v>
       </c>
       <c r="K18" t="n">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="M18" t="n">
-        <v>3.571</v>
+        <v>3.0446</v>
       </c>
       <c r="N18" t="n">
-        <v>170</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7497</v>
+        <v>2.8675</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5225</v>
+        <v>1.5877</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7497</v>
+        <v>2.8675</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4421</v>
+        <v>2.4424</v>
       </c>
       <c r="G19" t="n">
         <v>0.3076</v>
       </c>
       <c r="H19" t="n">
-        <v>2.62</v>
+        <v>2.6207</v>
       </c>
       <c r="I19" t="n">
-        <v>2.62</v>
+        <v>2.6207</v>
       </c>
       <c r="J19" t="n">
         <v>0.3076</v>
@@ -1311,7 +1311,7 @@
         <v>60</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9276</v>
+        <v>2.9283</v>
       </c>
       <c r="N19" t="n">
         <v>143</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6926</v>
+        <v>2.8258</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4909</v>
+        <v>1.5646</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6015</v>
+        <v>0.6484</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6926</v>
+        <v>2.8258</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4977</v>
+        <v>2.623</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1949</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4977</v>
+        <v>3.0159</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4977</v>
+        <v>3.0159</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1949</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L20" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6926</v>
+        <v>3.0159</v>
       </c>
       <c r="N20" t="n">
-        <v>337</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6683</v>
+        <v>2.6651</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4774</v>
+        <v>1.4757</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5905</v>
+        <v>0.5766</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6683</v>
+        <v>2.6651</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2813</v>
+        <v>2.282</v>
       </c>
       <c r="G21" t="n">
         <v>0.387</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2813</v>
+        <v>2.282</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2813</v>
+        <v>2.282</v>
       </c>
       <c r="J21" t="n">
         <v>0.387</v>
@@ -1403,7 +1403,7 @@
         <v>60</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6683</v>
+        <v>2.669</v>
       </c>
       <c r="N21" t="n">
         <v>143</v>
@@ -1412,78 +1412,78 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.623</v>
+        <v>2.6518</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4523</v>
+        <v>1.4683</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5698</v>
+        <v>0.5707</v>
       </c>
       <c r="E22" t="n">
-        <v>2.623</v>
+        <v>2.6518</v>
       </c>
       <c r="F22" t="n">
-        <v>2.623</v>
+        <v>1.4977</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1.1949</v>
       </c>
       <c r="H22" t="n">
-        <v>3.0159</v>
+        <v>1.4977</v>
       </c>
       <c r="I22" t="n">
-        <v>3.0159</v>
+        <v>1.4977</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.1949</v>
       </c>
       <c r="K22" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="M22" t="n">
-        <v>3.0159</v>
+        <v>2.6926</v>
       </c>
       <c r="N22" t="n">
-        <v>148</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5875</v>
+        <v>2.6426</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4327</v>
+        <v>1.4632</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5537</v>
+        <v>0.5666</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5875</v>
+        <v>2.6426</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5875</v>
+        <v>2.4295</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9384</v>
+        <v>2.5924</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9384</v>
+        <v>2.5924</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9384</v>
+        <v>2.5924</v>
       </c>
       <c r="N23" t="n">
         <v>159</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5028</v>
+        <v>2.6145</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3858</v>
+        <v>1.4476</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5151</v>
+        <v>0.554</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5028</v>
+        <v>2.6145</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5028</v>
+        <v>2.5875</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.7529</v>
+        <v>2.9384</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7529</v>
+        <v>2.9384</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7529</v>
+        <v>2.9384</v>
       </c>
       <c r="N24" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4958</v>
+        <v>2.528</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3819</v>
+        <v>1.3997</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5119</v>
+        <v>0.5154</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4958</v>
+        <v>2.528</v>
       </c>
       <c r="F25" t="n">
         <v>2.4958</v>
@@ -1596,415 +1596,415 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>degster</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4295</v>
+        <v>2.4788</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3452</v>
+        <v>1.3725</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4818</v>
+        <v>0.4934</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4295</v>
+        <v>2.4788</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4295</v>
+        <v>1.6737</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.7017</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5924</v>
+        <v>1.6737</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5924</v>
+        <v>1.7611</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.7017</v>
       </c>
       <c r="K26" t="n">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M26" t="n">
-        <v>2.5924</v>
+        <v>2.4628</v>
       </c>
       <c r="N26" t="n">
-        <v>159</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>degster</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.3754</v>
+        <v>2.4491</v>
       </c>
       <c r="C27" t="n">
-        <v>1.3153</v>
+        <v>1.3561</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4571</v>
+        <v>0.4801</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3754</v>
+        <v>2.4491</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6737</v>
+        <v>2.5028</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7017</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6737</v>
+        <v>2.7529</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7611</v>
+        <v>2.7529</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7017</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>246</v>
+        <v>179</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.4628</v>
+        <v>2.7529</v>
       </c>
       <c r="N27" t="n">
-        <v>316</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.177</v>
+        <v>2.3234</v>
       </c>
       <c r="C28" t="n">
-        <v>1.2054</v>
+        <v>1.2865</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3668</v>
+        <v>0.424</v>
       </c>
       <c r="E28" t="n">
-        <v>2.177</v>
+        <v>2.3234</v>
       </c>
       <c r="F28" t="n">
-        <v>2.177</v>
+        <v>2.1287</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.177</v>
+        <v>2.1287</v>
       </c>
       <c r="I28" t="n">
-        <v>2.177</v>
+        <v>2.1287</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.177</v>
+        <v>2.1287</v>
       </c>
       <c r="N28" t="n">
-        <v>204</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.1287</v>
+        <v>2.1571</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1787</v>
+        <v>1.1944</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3448</v>
+        <v>0.3497</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1287</v>
+        <v>2.1571</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1287</v>
+        <v>2.176</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1287</v>
+        <v>2.176</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1287</v>
+        <v>2.176</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.1287</v>
+        <v>2.176</v>
       </c>
       <c r="N29" t="n">
-        <v>117</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.066</v>
+        <v>2.0007</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1439</v>
+        <v>1.1078</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3163</v>
+        <v>0.2798</v>
       </c>
       <c r="E30" t="n">
-        <v>2.066</v>
+        <v>2.0007</v>
       </c>
       <c r="F30" t="n">
-        <v>2.066</v>
+        <v>0.4655</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="H30" t="n">
-        <v>2.066</v>
+        <v>0.4655</v>
       </c>
       <c r="I30" t="n">
-        <v>2.066</v>
+        <v>0.4655</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="K30" t="n">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M30" t="n">
-        <v>2.066</v>
+        <v>1.8255</v>
       </c>
       <c r="N30" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.0347</v>
+        <v>1.9932</v>
       </c>
       <c r="C31" t="n">
-        <v>1.1266</v>
+        <v>1.1036</v>
       </c>
       <c r="D31" t="n">
-        <v>0.302</v>
+        <v>0.2765</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0347</v>
+        <v>1.9932</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3511</v>
+        <v>2.066</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3164</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.421</v>
+        <v>2.066</v>
       </c>
       <c r="I31" t="n">
-        <v>2.421</v>
+        <v>2.066</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3164</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>124</v>
+        <v>179</v>
       </c>
       <c r="L31" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.1046</v>
+        <v>2.066</v>
       </c>
       <c r="N31" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8255</v>
+        <v>1.847</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0108</v>
+        <v>1.0227</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2068</v>
+        <v>0.2112</v>
       </c>
       <c r="E32" t="n">
-        <v>1.8255</v>
+        <v>1.847</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4655</v>
+        <v>2.3511</v>
       </c>
       <c r="G32" t="n">
-        <v>1.36</v>
+        <v>-0.3164</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4655</v>
+        <v>2.421</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4655</v>
+        <v>2.421</v>
       </c>
       <c r="J32" t="n">
-        <v>1.36</v>
+        <v>-0.3164</v>
       </c>
       <c r="K32" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L32" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.8255</v>
+        <v>2.1046</v>
       </c>
       <c r="N32" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.726</v>
+        <v>1.7688</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9557</v>
+        <v>0.9794</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1615</v>
+        <v>0.1763</v>
       </c>
       <c r="E33" t="n">
-        <v>1.726</v>
+        <v>1.7688</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3779</v>
+        <v>2.7121</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.6519</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>2.4796</v>
+        <v>3.2111</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4796</v>
+        <v>3.2111</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6519</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="L33" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="M33" t="n">
-        <v>1.8277</v>
+        <v>2.2111</v>
       </c>
       <c r="N33" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.7121</v>
+        <v>1.7522</v>
       </c>
       <c r="C34" t="n">
-        <v>0.948</v>
+        <v>0.9702</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1552</v>
+        <v>0.1688</v>
       </c>
       <c r="E34" t="n">
-        <v>1.7121</v>
+        <v>1.7522</v>
       </c>
       <c r="F34" t="n">
-        <v>2.7121</v>
+        <v>2.3721</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-0.6519</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2111</v>
+        <v>2.4668</v>
       </c>
       <c r="I34" t="n">
-        <v>3.2111</v>
+        <v>2.4668</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-0.6519</v>
       </c>
       <c r="K34" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="L34" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M34" t="n">
-        <v>2.2111</v>
+        <v>1.8149</v>
       </c>
       <c r="N34" t="n">
-        <v>180</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35">
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.7012</v>
+        <v>1.7212</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9419</v>
+        <v>0.953</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1502</v>
+        <v>0.155</v>
       </c>
       <c r="E35" t="n">
-        <v>1.7012</v>
+        <v>1.7212</v>
       </c>
       <c r="F35" t="n">
         <v>1.0723</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.6181</v>
+        <v>1.6146</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8959</v>
+        <v>0.894</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1124</v>
+        <v>0.1074</v>
       </c>
       <c r="E36" t="n">
-        <v>1.6181</v>
+        <v>1.6146</v>
       </c>
       <c r="F36" t="n">
-        <v>1.9915</v>
+        <v>1.6161</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.3734</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.9915</v>
+        <v>1.6161</v>
       </c>
       <c r="I36" t="n">
-        <v>2.0955</v>
+        <v>1.6161</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3734</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>246</v>
+        <v>204</v>
       </c>
       <c r="L36" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.7221</v>
+        <v>1.6161</v>
       </c>
       <c r="N36" t="n">
-        <v>316</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5821</v>
+        <v>1.5793</v>
       </c>
       <c r="C37" t="n">
-        <v>0.876</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.096</v>
+        <v>0.0916</v>
       </c>
       <c r="E37" t="n">
-        <v>1.5821</v>
+        <v>1.5793</v>
       </c>
       <c r="F37" t="n">
-        <v>1.5821</v>
+        <v>1.5511</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5821</v>
+        <v>1.5511</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5821</v>
+        <v>1.5511</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5821</v>
+        <v>1.5511</v>
       </c>
       <c r="N37" t="n">
-        <v>204</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.5801</v>
+        <v>1.5704</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8749</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0951</v>
+        <v>0.0876</v>
       </c>
       <c r="E38" t="n">
-        <v>1.5801</v>
+        <v>1.5704</v>
       </c>
       <c r="F38" t="n">
         <v>-1.8158</v>
@@ -2194,323 +2194,323 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.575</v>
+        <v>1.5513</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8721</v>
+        <v>0.859</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0791</v>
       </c>
       <c r="E39" t="n">
-        <v>1.575</v>
+        <v>1.5513</v>
       </c>
       <c r="F39" t="n">
-        <v>2.4387</v>
+        <v>1.4831</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8637</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.6126</v>
+        <v>1.4831</v>
       </c>
       <c r="I39" t="n">
-        <v>2.6126</v>
+        <v>1.4831</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8637</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="L39" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.7489</v>
+        <v>1.4831</v>
       </c>
       <c r="N39" t="n">
-        <v>293</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.5511</v>
+        <v>1.5434</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8588</v>
+        <v>0.8546</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0819</v>
+        <v>0.0756</v>
       </c>
       <c r="E40" t="n">
-        <v>1.5511</v>
+        <v>1.5434</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5511</v>
+        <v>1.9915</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.3734</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5511</v>
+        <v>1.9915</v>
       </c>
       <c r="I40" t="n">
-        <v>1.5511</v>
+        <v>2.0955</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.3734</v>
       </c>
       <c r="K40" t="n">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M40" t="n">
-        <v>1.5511</v>
+        <v>1.7221</v>
       </c>
       <c r="N40" t="n">
-        <v>179</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.4831</v>
+        <v>1.5372</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8212</v>
+        <v>0.8511</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0509</v>
+        <v>0.0728</v>
       </c>
       <c r="E41" t="n">
-        <v>1.4831</v>
+        <v>1.5372</v>
       </c>
       <c r="F41" t="n">
-        <v>1.4831</v>
+        <v>1.01</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="H41" t="n">
-        <v>1.4831</v>
+        <v>1.01</v>
       </c>
       <c r="I41" t="n">
-        <v>1.4831</v>
+        <v>1.036</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="K41" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4831</v>
+        <v>1.473</v>
       </c>
       <c r="N41" t="n">
-        <v>117</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.447</v>
+        <v>1.4064</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8012</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0345</v>
+        <v>0.0144</v>
       </c>
       <c r="E42" t="n">
-        <v>1.447</v>
+        <v>1.4064</v>
       </c>
       <c r="F42" t="n">
-        <v>1.01</v>
+        <v>1.7377</v>
       </c>
       <c r="G42" t="n">
-        <v>0.437</v>
+        <v>-0.4234</v>
       </c>
       <c r="H42" t="n">
-        <v>1.01</v>
+        <v>1.7377</v>
       </c>
       <c r="I42" t="n">
-        <v>1.036</v>
+        <v>1.7377</v>
       </c>
       <c r="J42" t="n">
-        <v>0.437</v>
+        <v>-0.4234</v>
       </c>
       <c r="K42" t="n">
-        <v>156</v>
+        <v>95</v>
       </c>
       <c r="L42" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="M42" t="n">
-        <v>1.473</v>
+        <v>1.3143</v>
       </c>
       <c r="N42" t="n">
-        <v>265</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.3285</v>
+        <v>1.397</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7356</v>
+        <v>0.7735</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0194</v>
+        <v>0.0102</v>
       </c>
       <c r="E43" t="n">
-        <v>1.3285</v>
+        <v>1.397</v>
       </c>
       <c r="F43" t="n">
-        <v>1.7069</v>
+        <v>2.4387</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.3784</v>
+        <v>-0.8637</v>
       </c>
       <c r="H43" t="n">
-        <v>1.7069</v>
+        <v>2.6126</v>
       </c>
       <c r="I43" t="n">
-        <v>1.7069</v>
+        <v>2.6126</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.3784</v>
+        <v>-0.8637</v>
       </c>
       <c r="K43" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="L43" t="n">
-        <v>119</v>
+        <v>167</v>
       </c>
       <c r="M43" t="n">
-        <v>1.3285</v>
+        <v>1.7489</v>
       </c>
       <c r="N43" t="n">
-        <v>214</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.3143</v>
+        <v>1.2786</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7277</v>
+        <v>0.708</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0259</v>
+        <v>-0.0427</v>
       </c>
       <c r="E44" t="n">
-        <v>1.3143</v>
+        <v>1.2786</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7377</v>
+        <v>1.2941</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.4234</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7377</v>
+        <v>1.2941</v>
       </c>
       <c r="I44" t="n">
-        <v>1.7377</v>
+        <v>1.2941</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.4234</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="L44" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.3143</v>
+        <v>1.2941</v>
       </c>
       <c r="N44" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.2853</v>
+        <v>1.2356</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7117</v>
+        <v>0.6841</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0391</v>
+        <v>-0.0619</v>
       </c>
       <c r="E45" t="n">
-        <v>1.2853</v>
+        <v>1.2356</v>
       </c>
       <c r="F45" t="n">
-        <v>1.2853</v>
+        <v>1.7069</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.3784</v>
       </c>
       <c r="H45" t="n">
-        <v>1.2853</v>
+        <v>1.7069</v>
       </c>
       <c r="I45" t="n">
-        <v>1.2853</v>
+        <v>1.7069</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.3784</v>
       </c>
       <c r="K45" t="n">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M45" t="n">
-        <v>1.2853</v>
+        <v>1.3285</v>
       </c>
       <c r="N45" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46">
@@ -2520,16 +2520,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.1438</v>
+        <v>1.1453</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6333</v>
+        <v>0.6341</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1035</v>
+        <v>-0.1022</v>
       </c>
       <c r="E46" t="n">
-        <v>1.1438</v>
+        <v>1.1453</v>
       </c>
       <c r="F46" t="n">
         <v>1.1438</v>
@@ -2562,553 +2562,553 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.1146</v>
+        <v>0.9968</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6172</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1168</v>
+        <v>-0.1686</v>
       </c>
       <c r="E47" t="n">
-        <v>1.1146</v>
+        <v>0.9968</v>
       </c>
       <c r="F47" t="n">
-        <v>1.7258</v>
+        <v>0.6853</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6112</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.7258</v>
+        <v>0.6853</v>
       </c>
       <c r="I47" t="n">
-        <v>1.7258</v>
+        <v>0.6853</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6112</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="L47" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.1146</v>
+        <v>0.6853</v>
       </c>
       <c r="N47" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.901</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4675</v>
+        <v>0.4989</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2399</v>
+        <v>-0.2114</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.901</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8473000000000001</v>
+        <v>1.7265</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.003</v>
+        <v>-0.6112</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8473000000000001</v>
+        <v>1.7265</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8473000000000001</v>
+        <v>1.7265</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.003</v>
+        <v>-0.6112</v>
       </c>
       <c r="K48" t="n">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="L48" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8443000000000001</v>
+        <v>1.1153</v>
       </c>
       <c r="N48" t="n">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.704</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3898</v>
+        <v>0.4703</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3037</v>
+        <v>-0.2345</v>
       </c>
       <c r="E49" t="n">
-        <v>0.704</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1031</v>
+        <v>0.4781</v>
       </c>
       <c r="G49" t="n">
-        <v>0.6009</v>
+        <v>0.2153</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1031</v>
+        <v>0.4781</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1031</v>
+        <v>0.4781</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6009</v>
+        <v>0.2153</v>
       </c>
       <c r="K49" t="n">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="L49" t="n">
-        <v>119</v>
+        <v>52</v>
       </c>
       <c r="M49" t="n">
-        <v>0.704</v>
+        <v>0.6934</v>
       </c>
       <c r="N49" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6934</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3839</v>
+        <v>0.4072</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3086</v>
+        <v>-0.2853</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6934</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4781</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2153</v>
+        <v>-0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4781</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4781</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>0.2153</v>
+        <v>-0.003</v>
       </c>
       <c r="K50" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="L50" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6934</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6853</v>
+        <v>0.7086</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3794</v>
+        <v>0.3923</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3122</v>
+        <v>-0.2973</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6853</v>
+        <v>0.7086</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6853</v>
+        <v>0.5319</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6853</v>
+        <v>0.5319</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6853</v>
+        <v>0.5319</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6853</v>
+        <v>0.5319</v>
       </c>
       <c r="N51" t="n">
-        <v>104</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6169</v>
+        <v>0.7025</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3416</v>
+        <v>0.389</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3434</v>
+        <v>-0.3</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6169</v>
+        <v>0.7025</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6169</v>
+        <v>0.3528</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6169</v>
+        <v>0.3528</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6169</v>
+        <v>0.3528</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6169</v>
+        <v>0.3528</v>
       </c>
       <c r="N52" t="n">
-        <v>204</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5319</v>
+        <v>0.6916</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2945</v>
+        <v>0.3829</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3821</v>
+        <v>-0.3049</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5319</v>
+        <v>0.6916</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5319</v>
+        <v>0.1031</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.6009</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5319</v>
+        <v>0.1031</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5319</v>
+        <v>0.1031</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.6009</v>
       </c>
       <c r="K53" t="n">
-        <v>148</v>
+        <v>95</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5319</v>
+        <v>0.704</v>
       </c>
       <c r="N53" t="n">
-        <v>148</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6716</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2844</v>
+        <v>0.3719</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3904</v>
+        <v>-0.3138</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.6716</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.3091</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.3091</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.3091</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.3091</v>
       </c>
       <c r="N54" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3579</v>
+        <v>0.5606</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1982</v>
+        <v>0.3104</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4613</v>
+        <v>-0.3634</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3579</v>
+        <v>0.5606</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3579</v>
+        <v>0.6271</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3579</v>
+        <v>0.6271</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3579</v>
+        <v>0.6271</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3579</v>
+        <v>0.6271</v>
       </c>
       <c r="N55" t="n">
-        <v>175</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3528</v>
+        <v>0.4857</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1953</v>
+        <v>0.2689</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4636</v>
+        <v>-0.3969</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3528</v>
+        <v>0.4857</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3528</v>
+        <v>0.3579</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3528</v>
+        <v>0.3579</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3528</v>
+        <v>0.3579</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3528</v>
+        <v>0.3579</v>
       </c>
       <c r="N56" t="n">
-        <v>106</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3091</v>
+        <v>0.438</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1711</v>
+        <v>0.2425</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4835</v>
+        <v>-0.4182</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3091</v>
+        <v>0.438</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3091</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3091</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3091</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3091</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>phzy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.293</v>
+        <v>0.1483</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1622</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4908</v>
+        <v>-0.5476</v>
       </c>
       <c r="E58" t="n">
-        <v>0.293</v>
+        <v>0.1483</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4678</v>
+        <v>-0.008</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.1748</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4678</v>
+        <v>-0.008</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4678</v>
+        <v>-0.008</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.1748</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="L58" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.293</v>
+        <v>-0.008</v>
       </c>
       <c r="N58" t="n">
-        <v>293</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2201</v>
+        <v>0.1154</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1219</v>
+        <v>0.0639</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.524</v>
+        <v>-0.5623</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2201</v>
+        <v>0.1154</v>
       </c>
       <c r="F59" t="n">
         <v>0.2201</v>
@@ -3160,553 +3160,553 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sjuush</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0843</v>
+        <v>0.0172</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0467</v>
+        <v>0.0095</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5858</v>
+        <v>-0.6061</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0843</v>
+        <v>0.0172</v>
       </c>
       <c r="F60" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4678</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003</v>
+        <v>-0.1748</v>
       </c>
       <c r="H60" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4678</v>
       </c>
       <c r="I60" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.4678</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0003</v>
+        <v>-0.1748</v>
       </c>
       <c r="K60" t="n">
-        <v>246</v>
+        <v>126</v>
       </c>
       <c r="L60" t="n">
-        <v>70</v>
+        <v>167</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0887</v>
+        <v>0.293</v>
       </c>
       <c r="N60" t="n">
-        <v>316</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>phzy</t>
+          <t>sjuush</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.008</v>
+        <v>-0.0968</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0044</v>
+        <v>-0.0536</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6278</v>
+        <v>-0.6571</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.008</v>
+        <v>-0.0968</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.008</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.008</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.008</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="K61" t="n">
-        <v>106</v>
+        <v>246</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.008</v>
+        <v>0.0887</v>
       </c>
       <c r="N61" t="n">
-        <v>106</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0881</v>
+        <v>-0.16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0488</v>
+        <v>-0.0886</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6643</v>
+        <v>-0.6853</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0881</v>
+        <v>-0.16</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0881</v>
+        <v>-0.2874</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0881</v>
+        <v>-0.2874</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0881</v>
+        <v>-0.2874</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.0881</v>
+        <v>-0.2874</v>
       </c>
       <c r="N62" t="n">
-        <v>179</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.1326</v>
+        <v>-0.2055</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.1138</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6846</v>
+        <v>-0.7056</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1326</v>
+        <v>-0.2055</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4924</v>
+        <v>-0.0881</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.625</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4924</v>
+        <v>-0.0881</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4924</v>
+        <v>-0.0881</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.625</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="L63" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.1326</v>
+        <v>-0.0881</v>
       </c>
       <c r="N63" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.1841</v>
+        <v>-0.2294</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1019</v>
+        <v>-0.127</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.708</v>
+        <v>-0.7163</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.1841</v>
+        <v>-0.2294</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1841</v>
+        <v>0.4924</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.625</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1841</v>
+        <v>0.4924</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1841</v>
+        <v>0.4924</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.625</v>
       </c>
       <c r="K64" t="n">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.1841</v>
+        <v>-0.1326</v>
       </c>
       <c r="N64" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.239</v>
+        <v>-0.2737</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1323</v>
+        <v>-0.1515</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.733</v>
+        <v>-0.7361</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.239</v>
+        <v>-0.2737</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.239</v>
+        <v>-0.1841</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.239</v>
+        <v>-0.1841</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.239</v>
+        <v>-0.1841</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.239</v>
+        <v>-0.1841</v>
       </c>
       <c r="N65" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.2717</v>
+        <v>-0.2815</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1504</v>
+        <v>-0.1559</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7479</v>
+        <v>-0.7396</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.2717</v>
+        <v>-0.2815</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2717</v>
+        <v>-0.239</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2717</v>
+        <v>-0.239</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2717</v>
+        <v>-0.239</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.2717</v>
+        <v>-0.239</v>
       </c>
       <c r="N66" t="n">
-        <v>159</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.2874</v>
+        <v>-0.4121</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1591</v>
+        <v>-0.2282</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.755</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2874</v>
+        <v>-0.4121</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.2874</v>
+        <v>-0.5995</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.2874</v>
+        <v>-0.5995</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.2874</v>
+        <v>-0.5995</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.2874</v>
+        <v>-0.5995</v>
       </c>
       <c r="N67" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.3784</v>
+        <v>-0.5152</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2095</v>
+        <v>-0.2853</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7965</v>
+        <v>-0.8439</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3784</v>
+        <v>-0.5152</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3784</v>
+        <v>-0.2717</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3784</v>
+        <v>-0.2717</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.3784</v>
+        <v>-0.2717</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.3784</v>
+        <v>-0.2717</v>
       </c>
       <c r="N68" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.415</v>
+        <v>-0.5255</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2298</v>
+        <v>-0.291</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8131</v>
+        <v>-0.8485</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.415</v>
+        <v>-0.5255</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.415</v>
+        <v>-0.3784</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.415</v>
+        <v>-0.3784</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.415</v>
+        <v>-0.3784</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.415</v>
+        <v>-0.3784</v>
       </c>
       <c r="N69" t="n">
-        <v>106</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.4209</v>
+        <v>-0.5732</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2331</v>
+        <v>-0.3174</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8158</v>
+        <v>-0.8699</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.4209</v>
+        <v>-0.5732</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.4209</v>
+        <v>-0.4228</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.4209</v>
+        <v>-0.4228</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4209</v>
+        <v>-0.4228</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.4209</v>
+        <v>-0.4228</v>
       </c>
       <c r="N70" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.4228</v>
+        <v>-0.6912</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2341</v>
+        <v>-0.3827</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8167</v>
+        <v>-0.9226</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.4228</v>
+        <v>-0.6912</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.4228</v>
+        <v>-0.4209</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.4228</v>
+        <v>-0.4209</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4228</v>
+        <v>-0.4209</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.4228</v>
+        <v>-0.4209</v>
       </c>
       <c r="N71" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
     </row>
     <row r="72">
@@ -3716,16 +3716,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.4714</v>
+        <v>-0.6924</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.261</v>
+        <v>-0.3834</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8388</v>
+        <v>-0.9231</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.4714</v>
+        <v>-0.6924</v>
       </c>
       <c r="F72" t="n">
         <v>-0.757</v>
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.4812</v>
+        <v>-0.7076</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2664</v>
+        <v>-0.3918</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8433</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.4812</v>
+        <v>-0.7076</v>
       </c>
       <c r="F73" t="n">
         <v>-0.4812</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.5995</v>
+        <v>-0.746</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.3319</v>
+        <v>-0.4131</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8971</v>
+        <v>-0.947</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.5995</v>
+        <v>-0.746</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.5995</v>
+        <v>-0.415</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.5995</v>
+        <v>-0.415</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.5995</v>
+        <v>-0.415</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.5995</v>
+        <v>-0.415</v>
       </c>
       <c r="N74" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75">
@@ -3854,16 +3854,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.7537</v>
+        <v>-0.782</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4173</v>
+        <v>-0.433</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9673</v>
+        <v>-0.9631</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7537</v>
+        <v>-0.782</v>
       </c>
       <c r="F75" t="n">
         <v>-0.7537</v>
@@ -3896,32 +3896,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>rigoN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2421</v>
+        <v>-1.5502</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6877</v>
+        <v>-0.8583</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1896</v>
+        <v>-1.3063</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2421</v>
+        <v>-1.5502</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.2421</v>
+        <v>-1.3968</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.2421</v>
+        <v>-1.3968</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.2421</v>
+        <v>-1.3968</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2421</v>
+        <v>-1.3968</v>
       </c>
       <c r="N76" t="n">
         <v>104</v>
@@ -3942,32 +3942,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rigoN</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3968</v>
+        <v>-1.5938</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7734</v>
+        <v>-0.8825</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2601</v>
+        <v>-1.3257</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3968</v>
+        <v>-1.5938</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3968</v>
+        <v>-1.2421</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3968</v>
+        <v>-1.2421</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3968</v>
+        <v>-1.2421</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3968</v>
+        <v>-1.2421</v>
       </c>
       <c r="N77" t="n">
         <v>104</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.4815</v>
+        <v>-1.958</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8203</v>
+        <v>-1.0841</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2986</v>
+        <v>-1.4884</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.4815</v>
+        <v>-1.958</v>
       </c>
       <c r="F78" t="n">
         <v>-1.4815</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.8634</v>
+        <v>-3.0629</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.5855</v>
+        <v>-1.6959</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.9277</v>
+        <v>-1.982</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.8634</v>
+        <v>-3.0629</v>
       </c>
       <c r="F79" t="n">
         <v>-2.8634</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.8934</v>
+        <v>-3.3846</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6021</v>
+        <v>-1.874</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.9413</v>
+        <v>-2.1256</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.8934</v>
+        <v>-3.3846</v>
       </c>
       <c r="F80" t="n">
         <v>-2.8934</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.8138</v>
+        <v>-4.1587</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.1117</v>
+        <v>-2.3027</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.3603</v>
+        <v>-2.4714</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.8138</v>
+        <v>-4.1587</v>
       </c>
       <c r="F81" t="n">
         <v>-1.4151</v>
@@ -29066,13 +29066,13 @@
         <v>29</v>
       </c>
       <c r="H622" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="I622" t="n">
-        <v>1.1357</v>
+        <v>1.1229</v>
       </c>
       <c r="J622" t="n">
-        <v>32.9353</v>
+        <v>32.5641</v>
       </c>
     </row>
     <row r="623">
@@ -29106,13 +29106,13 @@
         <v>29</v>
       </c>
       <c r="H623" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="I623" t="n">
-        <v>1.0663</v>
+        <v>1.0526</v>
       </c>
       <c r="J623" t="n">
-        <v>30.9227</v>
+        <v>30.5254</v>
       </c>
     </row>
     <row r="624">
@@ -29149,10 +29149,10 @@
         <v>1.07</v>
       </c>
       <c r="I624" t="n">
-        <v>0.2317</v>
+        <v>0.2324</v>
       </c>
       <c r="J624" t="n">
-        <v>6.7193</v>
+        <v>6.7396</v>
       </c>
     </row>
     <row r="625">
@@ -29189,10 +29189,10 @@
         <v>1.02</v>
       </c>
       <c r="I625" t="n">
-        <v>0.0708</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J625" t="n">
-        <v>2.0532</v>
+        <v>2.0735</v>
       </c>
     </row>
     <row r="626">
@@ -29229,10 +29229,10 @@
         <v>0.83</v>
       </c>
       <c r="I626" t="n">
-        <v>-0.5523</v>
+        <v>-0.5516</v>
       </c>
       <c r="J626" t="n">
-        <v>-16.0167</v>
+        <v>-15.9964</v>
       </c>
     </row>
     <row r="627">
@@ -29266,13 +29266,13 @@
         <v>29</v>
       </c>
       <c r="H627" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I627" t="n">
-        <v>0.3318</v>
+        <v>0.3658</v>
       </c>
       <c r="J627" t="n">
-        <v>9.622199999999999</v>
+        <v>10.6082</v>
       </c>
     </row>
     <row r="628">
@@ -29306,13 +29306,13 @@
         <v>29</v>
       </c>
       <c r="H628" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I628" t="n">
-        <v>0.3133</v>
+        <v>0.3297</v>
       </c>
       <c r="J628" t="n">
-        <v>9.085699999999999</v>
+        <v>9.561299999999999</v>
       </c>
     </row>
     <row r="629">
@@ -29349,10 +29349,10 @@
         <v>1</v>
       </c>
       <c r="I629" t="n">
-        <v>0.0016</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J629" t="n">
-        <v>0.0464</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="630">
@@ -29386,13 +29386,13 @@
         <v>29</v>
       </c>
       <c r="H630" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I630" t="n">
-        <v>-0.1677</v>
+        <v>-0.1575</v>
       </c>
       <c r="J630" t="n">
-        <v>-4.8633</v>
+        <v>-4.5675</v>
       </c>
     </row>
     <row r="631">
@@ -29426,13 +29426,13 @@
         <v>29</v>
       </c>
       <c r="H631" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.2898</v>
+        <v>-0.281</v>
       </c>
       <c r="J631" t="n">
-        <v>-8.404199999999999</v>
+        <v>-8.148999999999999</v>
       </c>
     </row>
     <row r="632">
